--- a/data/gravel/Chumba Terlingua Steel 2025.xlsx
+++ b/data/gravel/Chumba Terlingua Steel 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10824"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel incomplete/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{48C23158-626F-2344-92AF-D8B9F824C3BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E735EDCA-9093-EC4A-833A-3785FDCCD3FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3660" yWindow="2360" windowWidth="25140" windowHeight="13220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="34380" yWindow="-24740" windowWidth="25140" windowHeight="13220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="114">
   <si>
     <t>brand</t>
   </si>
@@ -302,9 +302,6 @@
     <t>yes</t>
   </si>
   <si>
-    <t>usd</t>
-  </si>
-  <si>
     <t>Measurement</t>
   </si>
   <si>
@@ -372,6 +369,12 @@
   </si>
   <si>
     <t>Terlingua Steel (short)</t>
+  </si>
+  <si>
+    <t>USD</t>
+  </si>
+  <si>
+    <t>https://images.squarespace-cdn.com/content/v1/52f98c74e4b097d8674dc15e/1725976712625-5UQH5G41JVP338NW0UFF/Bikepacking-Roots-Chumba-Terlingua-Gravel-Giveaway-Bike4.jpg?format=1500w</t>
   </si>
 </sst>
 </file>
@@ -730,7 +733,7 @@
         <v>2</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.3">
@@ -757,6 +760,11 @@
         <v>85</v>
       </c>
     </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>113</v>
+      </c>
+    </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>6</v>
@@ -770,7 +778,7 @@
         <v>8</v>
       </c>
       <c r="B8" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="C8">
         <v>50</v>
@@ -848,7 +856,7 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="C11">
         <v>100</v>
@@ -953,22 +961,22 @@
         <v>425</v>
       </c>
       <c r="I14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="J14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="K14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="L14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="M14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="N14" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.3">
@@ -1029,22 +1037,22 @@
         <v>1053</v>
       </c>
       <c r="I16" t="s">
+        <v>99</v>
+      </c>
+      <c r="J16" t="s">
         <v>100</v>
       </c>
-      <c r="J16" t="s">
+      <c r="K16" t="s">
         <v>101</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>102</v>
       </c>
-      <c r="L16" t="s">
+      <c r="M16" t="s">
         <v>103</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" t="s">
         <v>104</v>
-      </c>
-      <c r="N16" t="s">
-        <v>105</v>
       </c>
     </row>
     <row r="17" spans="1:8" x14ac:dyDescent="0.3">
@@ -1369,25 +1377,25 @@
         <v>80</v>
       </c>
       <c r="C33" t="s">
+        <v>91</v>
+      </c>
+      <c r="D33" t="s">
         <v>92</v>
       </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>93</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>94</v>
       </c>
-      <c r="F33" t="s">
+      <c r="G33" t="s">
         <v>95</v>
       </c>
-      <c r="G33" t="s">
+      <c r="H33" t="s">
         <v>96</v>
       </c>
-      <c r="H33" t="s">
-        <v>97</v>
-      </c>
       <c r="I33" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
@@ -1398,22 +1406,22 @@
         <v>82</v>
       </c>
       <c r="C34" t="s">
+        <v>105</v>
+      </c>
+      <c r="D34" t="s">
         <v>106</v>
       </c>
-      <c r="D34" t="s">
+      <c r="E34" t="s">
         <v>107</v>
       </c>
-      <c r="E34" t="s">
+      <c r="F34" t="s">
         <v>108</v>
       </c>
-      <c r="F34" t="s">
+      <c r="G34" t="s">
         <v>109</v>
       </c>
-      <c r="G34" t="s">
+      <c r="H34" t="s">
         <v>110</v>
-      </c>
-      <c r="H34" t="s">
-        <v>111</v>
       </c>
       <c r="I34" t="s">
         <v>25</v>
@@ -1641,7 +1649,7 @@
         <v>78</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>89</v>
+        <v>112</v>
       </c>
     </row>
   </sheetData>

--- a/data/gravel/Chumba Terlingua Steel 2025.xlsx
+++ b/data/gravel/Chumba Terlingua Steel 2025.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E735EDCA-9093-EC4A-833A-3785FDCCD3FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{162F893B-B6FF-5949-AFA4-951DD96E75EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34380" yWindow="-24740" windowWidth="25140" windowHeight="13220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="116">
   <si>
     <t>brand</t>
   </si>
@@ -375,6 +375,12 @@
   </si>
   <si>
     <t>https://images.squarespace-cdn.com/content/v1/52f98c74e4b097d8674dc15e/1725976712625-5UQH5G41JVP338NW0UFF/Bikepacking-Roots-Chumba-Terlingua-Gravel-Giveaway-Bike4.jpg?format=1500w</t>
+  </si>
+  <si>
+    <t>location</t>
+  </si>
+  <si>
+    <t>Kansas City, Missouri, USA</t>
   </si>
 </sst>
 </file>
@@ -714,7 +720,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N70"/>
+  <dimension ref="A1:N71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1652,6 +1658,14 @@
         <v>112</v>
       </c>
     </row>
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A71" t="s">
+        <v>114</v>
+      </c>
+      <c r="B71" t="s">
+        <v>115</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>

--- a/data/gravel/Chumba Terlingua Steel 2025.xlsx
+++ b/data/gravel/Chumba Terlingua Steel 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{162F893B-B6FF-5949-AFA4-951DD96E75EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3009C885-ABE9-7C4A-B0DE-0B67A5F830C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34380" yWindow="-24740" windowWidth="25140" windowHeight="13220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="116">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -381,6 +381,9 @@
   </si>
   <si>
     <t>Kansas City, Missouri, USA</t>
+  </si>
+  <si>
+    <t>optional</t>
   </si>
 </sst>
 </file>
@@ -1583,6 +1586,9 @@
       <c r="A57" t="s">
         <v>65</v>
       </c>
+      <c r="B57" s="1" t="s">
+        <v>116</v>
+      </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">

--- a/data/gravel/Chumba Terlingua Steel 2025.xlsx
+++ b/data/gravel/Chumba Terlingua Steel 2025.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3009C885-ABE9-7C4A-B0DE-0B67A5F830C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2575915-65C7-0747-A76F-EFEF1D3AC872}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="34380" yWindow="-24740" windowWidth="25140" windowHeight="13220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="134" uniqueCount="123">
   <si>
     <t>brand</t>
   </si>
@@ -384,6 +384,24 @@
   </si>
   <si>
     <t>optional</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -723,7 +741,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N71"/>
+  <dimension ref="A1:N77"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="19.6640625" customWidth="1"/>
@@ -1513,162 +1531,192 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>55</v>
-      </c>
-      <c r="B47" s="1" t="s">
-        <v>86</v>
+        <v>117</v>
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>56</v>
+        <v>118</v>
       </c>
     </row>
     <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>57</v>
-      </c>
-      <c r="B49">
-        <v>27.2</v>
+        <v>119</v>
       </c>
     </row>
     <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>58</v>
+        <v>120</v>
       </c>
     </row>
     <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>59</v>
-      </c>
-      <c r="B51">
-        <v>46</v>
+        <v>121</v>
       </c>
     </row>
     <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>60</v>
-      </c>
-      <c r="B52">
-        <v>52</v>
+        <v>122</v>
       </c>
     </row>
     <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>61</v>
-      </c>
-      <c r="B53">
-        <v>160</v>
+        <v>55</v>
+      </c>
+      <c r="B53" s="1" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>62</v>
-      </c>
-      <c r="B54">
-        <v>160</v>
+        <v>56</v>
       </c>
     </row>
     <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>63</v>
+        <v>57</v>
+      </c>
+      <c r="B55">
+        <v>27.2</v>
       </c>
     </row>
     <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>64</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
     </row>
     <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>65</v>
-      </c>
-      <c r="B57" s="1" t="s">
-        <v>116</v>
+        <v>59</v>
+      </c>
+      <c r="B57">
+        <v>46</v>
       </c>
     </row>
     <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>66</v>
+        <v>60</v>
+      </c>
+      <c r="B58">
+        <v>52</v>
       </c>
     </row>
     <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>67</v>
+        <v>61</v>
+      </c>
+      <c r="B59">
+        <v>160</v>
       </c>
     </row>
     <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="B60">
+        <v>160</v>
       </c>
     </row>
     <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>69</v>
+        <v>63</v>
       </c>
     </row>
     <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>70</v>
+        <v>64</v>
+      </c>
+      <c r="B62" s="1" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>71</v>
+        <v>65</v>
+      </c>
+      <c r="B63" s="1" t="s">
+        <v>116</v>
       </c>
     </row>
     <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
     </row>
     <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
     </row>
     <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>75</v>
-      </c>
-      <c r="B67">
-        <v>2320</v>
+        <v>69</v>
       </c>
     </row>
     <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
     </row>
     <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>77</v>
-      </c>
-      <c r="B69" s="1" t="s">
-        <v>88</v>
+        <v>71</v>
       </c>
     </row>
     <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>78</v>
-      </c>
-      <c r="B70" s="1" t="s">
-        <v>112</v>
+        <v>72</v>
       </c>
     </row>
     <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A72" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>75</v>
+      </c>
+      <c r="B73">
+        <v>2320</v>
+      </c>
+    </row>
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A75" t="s">
+        <v>77</v>
+      </c>
+      <c r="B75" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A76" t="s">
+        <v>78</v>
+      </c>
+      <c r="B76" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A77" t="s">
         <v>114</v>
       </c>
-      <c r="B71" t="s">
+      <c r="B77" t="s">
         <v>115</v>
       </c>
     </row>
